--- a/backend/ATH_Open_Sheets_Template.xlsx
+++ b/backend/ATH_Open_Sheets_Template.xlsx
@@ -1196,14 +1196,10 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Cora</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Williams</t>
-        </is>
-      </c>
+          <t>Alexis</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr">
         <is>
           <t>B</t>
@@ -1220,20 +1216,12 @@
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>(555)200-0001</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>cora@example.com</t>
-        </is>
-      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>b8</t>
+          <t>b6</t>
         </is>
       </c>
     </row>
@@ -1245,14 +1233,10 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Sofia</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Reyes</t>
-        </is>
-      </c>
+          <t>Carmela</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
       <c r="D16" s="4" t="inlineStr">
         <is>
           <t>B</t>
@@ -1269,20 +1253,12 @@
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>(555)200-0009</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>sofia@example.com</t>
-        </is>
-      </c>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
       <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>b11</t>
+          <t>b3</t>
         </is>
       </c>
     </row>
@@ -1294,14 +1270,10 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Maria</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
+          <t>Ivy</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr">
         <is>
           <t>B</t>
@@ -1318,16 +1290,8 @@
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>(555)200-0010</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>maria@example.com</t>
-        </is>
-      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
@@ -1343,14 +1307,10 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Jensen</t>
-        </is>
-      </c>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
       <c r="D18" s="4" t="inlineStr">
         <is>
           <t>B</t>
@@ -1367,16 +1327,8 @@
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>(555)200-0002</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>paul@example.com</t>
-        </is>
-      </c>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr"/>
       <c r="J18" s="4" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr"/>
     </row>
@@ -1388,14 +1340,10 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Raj</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
+          <t>Marv</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="4" t="inlineStr">
         <is>
           <t>B</t>
@@ -1412,18 +1360,14 @@
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>(555)200-0003</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>raj@example.com</t>
-        </is>
-      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
       <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>b9</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1433,14 +1377,10 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Tom</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Nguyen</t>
-        </is>
-      </c>
+          <t>Arman</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
       <c r="D20" s="4" t="inlineStr">
         <is>
           <t>B</t>
@@ -1457,16 +1397,8 @@
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>(555)200-0004</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>tom@example.com</t>
-        </is>
-      </c>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr"/>
     </row>
@@ -1478,14 +1410,10 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Eric</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Hall</t>
-        </is>
-      </c>
+          <t>Jon</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="inlineStr">
         <is>
           <t>B</t>
@@ -1502,16 +1430,8 @@
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>(555)200-0005</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>eric@example.com</t>
-        </is>
-      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr"/>
     </row>
@@ -1523,14 +1443,10 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Diego</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Castro</t>
-        </is>
-      </c>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
       <c r="D22" s="4" t="inlineStr">
         <is>
           <t>B</t>
@@ -1547,18 +1463,14 @@
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>(555)200-0006</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>diego@example.com</t>
-        </is>
-      </c>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
       <c r="J22" s="4" t="inlineStr"/>
-      <c r="K22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1568,14 +1480,10 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Nathan</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Ford</t>
-        </is>
-      </c>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
       <c r="D23" s="4" t="inlineStr">
         <is>
           <t>B</t>
@@ -1592,16 +1500,8 @@
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>(555)200-0007</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>nathan@example.com</t>
-        </is>
-      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr"/>
     </row>
@@ -1613,14 +1513,10 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Omar</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Diallo</t>
-        </is>
-      </c>
+          <t>Rhon</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr"/>
       <c r="D24" s="4" t="inlineStr">
         <is>
           <t>B</t>
@@ -1637,22 +1533,10 @@
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>(555)200-0008</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>omar@example.com</t>
-        </is>
-      </c>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
       <c r="J24" s="4" t="inlineStr"/>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
+      <c r="K24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1662,14 +1546,10 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Carlos</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Reyes</t>
-        </is>
-      </c>
+          <t>Joe</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="4" t="inlineStr">
         <is>
           <t>B</t>
@@ -1686,22 +1566,10 @@
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>(555)200-0011</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>carlos@example.com</t>
-        </is>
-      </c>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
       <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>b9</t>
-        </is>
-      </c>
+      <c r="K25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1711,14 +1579,10 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>James</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr"/>
       <c r="D26" s="4" t="inlineStr">
         <is>
           <t>B</t>
@@ -1735,16 +1599,8 @@
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>(555)200-0012</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>james@example.com</t>
-        </is>
-      </c>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr"/>
       <c r="J26" s="4" t="inlineStr"/>
       <c r="K26" s="4" t="inlineStr">
         <is>
@@ -1763,7 +1619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1925,54 +1781,54 @@
       <c r="I5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>m5</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>m6</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2000,54 +1856,54 @@
       <c r="I8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>m8</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>m9</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2075,104 +1931,104 @@
       <c r="I11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>m11</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>m12</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>m13</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr"/>
-      <c r="G12" s="6" t="inlineStr"/>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>m12</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>m14</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>m13</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>m14</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2223,6 +2079,56 @@
       <c r="G17" s="5" t="inlineStr"/>
       <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>m17</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>m18</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2238,7 +2144,7 @@
   <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2412,7 +2318,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>TRUE = Mixed Doubles ★  (yellow rows). Pre-filled.</t>
+          <t>TRUE = Mixed Doubles ★ (yellow rows). Pre-filled.</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2330,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Team A player IDs for this match (copy from Players tab column A)</t>
+          <t>Team A player IDs for this match — copy from Players tab column A</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2377,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Players with a partnerId play together in all Mixed Doubles matches (★ rows).</t>
+          <t>Players with a partnerId play together in all Mixed Doubles (★) matches.</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2389,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Captain plays 1 mixed doubles game (round 4 South). Her partner plays 1 mixed + 2 men's.</t>
+          <t>Captain plays 1 mixed game (round 4 South). Her partner: 1 mixed + 2 men's.</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2401,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Each plays 2 mixed doubles games (rounds 3 and 6). Their partners play 2 mixed + 1 men's.</t>
+          <t>Each plays 2 mixed games (rounds 3 and 6). Their partners: 2 mixed + 1 men's.</t>
         </is>
       </c>
     </row>

--- a/backend/ATH_Open_Sheets_Template.xlsx
+++ b/backend/ATH_Open_Sheets_Template.xlsx
@@ -32,15 +32,11 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00888888"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <b val="1"/>
     </font>
+    <font/>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -54,17 +50,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFDCE0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EDE7F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00DCE8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -104,13 +105,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -118,17 +119,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -494,20 +496,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -567,673 +569,452 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>auto-generated</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>A or B</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>M or F</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>TRUE/FALSE</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>optional URL</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>auto-generated</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>partner's id or blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>a1</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Suzan</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>King</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>(555)100-0001</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>suzan@example.com</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>a2</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Molly</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>a4</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>a5</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Jeff</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a6</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Dro</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>a7</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>a8</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Mich</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>a9</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Rachel</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Park</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Wilfred</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>a10</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Jeff</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>a11</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Yu Fon</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>a12</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Johnny</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>b13</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Cora</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>(555)100-0009</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>rachel@example.com</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>a11</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>a10</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Lisa</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Torres</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>(555)100-0010</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>lisa@example.com</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>a12</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>a2</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Marcus</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Rivera</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>(555)100-0002</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>marcus@example.com</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>a3</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Derek</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Pham</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>(555)100-0003</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>derek@example.com</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>a4</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>James</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Okafor</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>(555)100-0004</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>james@example.com</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>a5</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Luis</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Chen</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>(555)100-0005</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>luis@example.com</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>a6</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Tyler</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Brooks</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>(555)100-0006</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>tyler@example.com</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>a7</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Marsh</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>(555)100-0007</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>kevin@example.com</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>a8</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Andre</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>(555)100-0008</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>andre@example.com</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>a11</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Ryan</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Park</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>(555)100-0011</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>ryan@example.com</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>a12</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Brian</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Torres</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>(555)100-0012</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>brian@example.com</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>a10</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>b1</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Alexis</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>b9</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Carmela</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -1258,19 +1039,19 @@
       <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
+          <t>b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>b10</t>
+          <t>b9</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ivy</t>
+          <t>Carmela</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -1295,19 +1076,19 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>b12</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+          <t>b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>b2</t>
+          <t>b10</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Jay</t>
+          <t>Ivy</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -1318,7 +1099,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1330,17 +1111,21 @@
       <c r="H18" s="4" t="inlineStr"/>
       <c r="I18" s="4" t="inlineStr"/>
       <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>b12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>b3</t>
+          <t>b2</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Marv</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -1363,21 +1148,17 @@
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr"/>
       <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+      <c r="K19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>b4</t>
+          <t>b3</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Arman</t>
+          <t>Marv</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -1400,17 +1181,21 @@
       <c r="H20" s="4" t="inlineStr"/>
       <c r="I20" s="4" t="inlineStr"/>
       <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>b5</t>
+          <t>b4</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Jon</t>
+          <t>Arman</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -1435,15 +1220,15 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr"/>
     </row>
-    <row r="22">
+    <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>b6</t>
+          <t>b5</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Jon</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -1466,21 +1251,17 @@
       <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr"/>
       <c r="J22" s="4" t="inlineStr"/>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+      <c r="K22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>b7</t>
+          <t>b6</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -1503,17 +1284,21 @@
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr"/>
       <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>b8</t>
+          <t>b7</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Rhon</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -1538,15 +1323,15 @@
       <c r="J24" s="4" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr"/>
     </row>
-    <row r="25">
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>b11</t>
+          <t>b8</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Joe</t>
+          <t>Rhon</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -1571,15 +1356,15 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr"/>
     </row>
-    <row r="26">
+    <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>b12</t>
+          <t>b11</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Joe</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -1602,7 +1387,40 @@
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr"/>
       <c r="J26" s="4" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>b12</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>b10</t>
         </is>
@@ -1619,18 +1437,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1679,8 +1499,18 @@
           <t>winner</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>scoreA</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>scoreB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>m1</t>
@@ -1699,13 +1529,31 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr"/>
-      <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>a4</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>a5</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>b6</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>b8</t>
+        </is>
+      </c>
       <c r="I2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>m2</t>
@@ -1724,13 +1572,31 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>a6</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>a7</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>b7</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>b11</t>
+        </is>
+      </c>
       <c r="I3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>m3</t>
@@ -1749,13 +1615,31 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>a8</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>a9</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>b12</t>
+        </is>
+      </c>
       <c r="I4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>m4</t>
@@ -1774,13 +1658,31 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>a10</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>a11</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>b5</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>m5</t>
@@ -1799,13 +1701,31 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>a7</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>a10</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>b8</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>b11</t>
+        </is>
+      </c>
       <c r="I6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>m6</t>
@@ -1824,13 +1744,31 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>a6</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>a12</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>b7</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>m7</t>
@@ -1849,13 +1787,31 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>a4</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>a1</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>b12</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>b10</t>
+        </is>
+      </c>
       <c r="I8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>m8</t>
@@ -1874,13 +1830,31 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>a5</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>a2</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>b9</t>
+        </is>
+      </c>
       <c r="I9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t>m9</t>
@@ -1899,13 +1873,31 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr"/>
-      <c r="G10" s="6" t="inlineStr"/>
-      <c r="H10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>a5</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>b6</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
       <c r="I10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11">
+      <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>m10</t>
@@ -1924,13 +1916,31 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>a12</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>a9</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>b8</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>m11</t>
@@ -1949,13 +1959,31 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>a11</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>a7</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>b7</t>
+        </is>
+      </c>
       <c r="I12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>m12</t>
@@ -1974,13 +2002,31 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>a4</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>a8</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>b5</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>b11</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t>m13</t>
@@ -1999,13 +2045,31 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>a12</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>a2</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>b13</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15">
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t>m14</t>
@@ -2024,13 +2088,31 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>a8</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>b12</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>b10</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16">
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>m15</t>
@@ -2049,13 +2131,31 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>a10</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>a6</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>b4</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>b11</t>
+        </is>
+      </c>
       <c r="I16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>m16</t>
@@ -2074,13 +2174,31 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>a11</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>a5</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>b5</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>b8</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t>m17</t>
@@ -2099,13 +2217,31 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr"/>
-      <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="6" t="inlineStr"/>
-      <c r="H18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>a9</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>a2</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>b6</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19">
+      <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t>m18</t>
@@ -2124,11 +2260,29 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>a4</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>b3</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>b9</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2141,311 +2295,359 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
+          <t>SETUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>1. Run initSheets()</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>In the Apps Script editor, select initSheets from the function dropdown and Run. This creates the Players and Schedule tabs and pre-populates all 18 matches. Do this ONCE before the tournament.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>2. Deploy as Web App</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Apps Script → Deploy → New deployment → Web app. Execute as: Me. Who has access: Anyone. Copy the /exec URL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>3. Set VITE_SHEETS_API_URL</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Paste the /exec URL into GitHub → Settings → Secrets → VITE_SHEETS_API_URL. Re-run the GitHub Actions workflow to rebuild.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="10" t="inlineStr"/>
+      <c r="B5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
           <t>PLAYERS TAB</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>Leave blank — auto-generated by the registration form (format: p&lt;timestamp&gt;)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Pre-assigned (a1–a12 for HSB, b1–b13 for Blue Crew). Registration form auto-generates p&lt;timestamp&gt; for new players.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>firstName / lastName</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Player's name</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>A  or  B</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>M  or  F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>isCaptain</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>TRUE for one player per team; FALSE for everyone else</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>headshotUrl</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Optional: direct link to a photo (JPEG or PNG)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>phone / email</t>
-        </is>
-      </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Optional contact info</t>
+          <t>Player's name. lastName can be blank (most players). Set lastName for disambiguation: Jeff E / Jeff W.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>team</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Leave blank — auto-filled when player registers via the web form</t>
+          <t>A (Hill Street Blues) or B (Blue Crew / JPL Team)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>M or F</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>isCaptain</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>TRUE for one player per team; FALSE for all others. Blue Crew captain = Cora (b13).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>headshotUrl</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Optional: direct URL to a portrait photo (JPEG or PNG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
           <t>partnerId</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>The id of this player's mixed doubles partner (e.g. a8). Leave blank if no partner playing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="8" t="inlineStr"/>
-      <c r="B11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>SCHEDULE TAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Match IDs m1–m16 are pre-filled. Do not change.</t>
+          <t>The id of this player's fixed mixed-doubles partner. Blank if no fixed partner. Examples: b6 for Alexis (her couple is Trevor), b13 for Cora (blank — Jay is not a fixed couple).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>round</t>
+          <t>phone / email</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Round number 1–8. Pre-filled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
+          <t>Optional. Not displayed on the site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>court</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>S = South Court, N = North Court. Pre-filled.</t>
+          <t>Auto-filled when a player registers via the web form. Leave blank for pre-loaded players.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>isMix</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>TRUE = Mixed Doubles ★ (yellow rows). Pre-filled.</t>
-        </is>
-      </c>
+      <c r="A16" s="10" t="inlineStr"/>
+      <c r="B16" s="9" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>teamAP1 / teamAP2</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Team A player IDs for this match — copy from Players tab column A</t>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>SCHEDULE TAB</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>teamBP1 / teamBP2</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Team B (Blue Crew) player IDs for this match</t>
+          <t>Match IDs m1–m18 are pre-filled. Do not change.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
+          <t>round / court</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Pre-filled. Round 1–9, court S (South) or N (North).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>isMix</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>TRUE = Mixed Doubles ★. Pre-filled. Yellow rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>teamAP1/AP2</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Hill Street Blues player IDs for this match. Pre-filled with the locked HSB pairings from their docx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>teamBP1/BP2</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Blue Crew player IDs for this match. Pre-filled with the generated pairings from generate_pairings.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>winner</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Enter A or B after the match is played. Or use the app Scores page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="inlineStr"/>
-      <c r="B20" s="9" t="inlineStr"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>COUPLES (Mixed Doubles)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>How it works</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Players with a partnerId play together in all Mixed Doubles (★) matches.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Captain</t>
-        </is>
-      </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Captain plays 1 mixed game (round 4 South). Her partner: 1 mixed + 2 men's.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
+          <t>Enter A or B after the match is played. Or use the app Scores page — the captain presses A Wins / B Wins on their phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Non-captain women</t>
+          <t>scoreA / scoreB</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Each plays 2 mixed games (rounds 3 and 6). Their partners: 2 mixed + 1 men's.</t>
+          <t>Optional numeric scores. Enter after the match, e.g. 11 and 9. The app shows these alongside the winner badge. The Scores page has numeric input fields in edit mode.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="8" t="inlineStr"/>
+      <c r="A25" s="10" t="inlineStr"/>
       <c r="B25" s="9" t="inlineStr"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>MEN'S DOUBLES</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
+          <t>LIVE UPDATES</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Pairing rule</t>
+          <t>How it works</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Each man plays exactly 3 games, never with the same partner twice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
+          <t>Once VITE_SHEETS_API_URL is set, the app reads from this sheet on every page load. No rebuild or redeploy needed — edit this sheet and the website updates immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Seeding</t>
+          <t>Roster changes</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>TBD — random draw or captain's choice. Fill teamAP1/AP2/BP1/BP2 before tournament day.</t>
+          <t>Add, edit, or remove players in the Players tab. Changes appear on the Teams page within seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Score entry</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Enter winner (A/B) and optional scores in the Schedule tab. Changes appear on the Scores and Schedule pages immediately. Captains can also enter scores directly in the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="10" t="inlineStr"/>
+      <c r="B30" s="9" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>PLAYER ID REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Hill Street Blues</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>a1=Suzan  a2=Rachel  a3=Molly  a4=Pierre  a5=Jeff E  a6=Dro  a7=Steve  a8=Mich  a9=Wilfred  a10=Jeff W  a11=Yu Fon  a12=Johnny</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Blue Crew</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>b13=Cora(C)  b1=Alexis  b9=Carmela  b10=Ivy  b2=Jay  b3=Marv  b4=Arman  b5=Jon  b6=Trevor  b7=Richard  b8=Rhon  b11=Joe  b12=Pierre</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/ATH_Open_Sheets_Template.xlsx
+++ b/backend/ATH_Open_Sheets_Template.xlsx
@@ -10,6 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Players" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Use" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HSB Pairings Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HSB Player Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blue Crew Matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blue Crew Player Summary" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +40,60 @@
       <b val="1"/>
     </font>
     <font/>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001B5E20"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007B4F00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="005E2CA5"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +135,31 @@
         <fgColor rgb="002d7d4f"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF176"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0E0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -105,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -131,6 +213,129 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2651,4 +2856,3187 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>ATH Open — Full Tournament Schedule  (Hill Street Blues  vs  Blue Crew / JPL Team)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Court</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>Hill Street Blues</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr"/>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>Blue Crew (JPL)</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr"/>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="13" t="n"/>
+      <c r="B3" s="13" t="n"/>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Player 1</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Player 2</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Player 1</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Player 2</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>S (South)</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Men's Doubles</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Jeff E</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Rhon</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>N (North)</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Men's Doubles</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Dro</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>Joe</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>8:50 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>S (South)</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Men's Doubles</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Mich</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Wilfred</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Arman</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>8:50 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>N (North)</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Men's Doubles</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Jeff W</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Yu Fon</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Marv</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>Jon</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>9:15 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>S (South)</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Men's Doubles</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>Jeff W</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Rhon</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>Joe</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>9:15 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>N (North)</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Men's Doubles</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Dro</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Johnny</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>9:40 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>S (South)</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Mix Doubles ★</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Suzan</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>Ivy</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>9:40 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>N (North)</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Mix Doubles ★</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Jeff E</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>Marv</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Carmela</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>10:10 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>S (South)</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Mix Doubles ★</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>Jeff E</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Molly</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>Alexis</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>10:10 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>N (North)</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Men's Doubles</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Johnny</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>Wilfred</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>Rhon</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>10:30 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>S (South)</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Men's Doubles</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Yu Fon</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Arman</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>10:30 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>N (North)</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Men's Doubles</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>Mich</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Jon</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>Joe</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>S (South)</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Mix Doubles ★</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Johnny</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>Cora</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>Captain's game ★</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>N (North)</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Mix Doubles ★</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>Mich</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Molly</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>Ivy</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>S (South)</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Men's Doubles</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Jeff W</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>Dro</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Arman</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>Joe</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>N (North)</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Men's Doubles</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Yu Fon</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Jeff E</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Jon</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>Rhon</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>S (South)</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Mix Doubles ★</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>Wilfred</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>Alexis</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>N (North)</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Mix Doubles ★</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Molly</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>Marv</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Carmela</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Hill Street Blues — Player Pairings Matrix   (X = Men's Doubles  |  M★ = Mixed Doubles)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Captain: Suzan  ·  No fixed couples  ·  3 women × 1–3 mixed games  ·  9 men × 3–4 games each</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>Pierre
+(M)</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Jeff E
+(M)</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>Dro
+(M)</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>Steve
+(M)</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>Mich
+(M)</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Wilfred
+(M)</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>Jeff W
+(M)</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>Yu Fon
+(M)</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>Johnny
+(M)</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>Suzan
+(F★) ©</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>Rachel
+(F★)</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>Molly
+(F★)</t>
+        </is>
+      </c>
+      <c r="O4" s="13" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="P4" s="13" t="inlineStr">
+        <is>
+          <t>Mix★</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>Pierre (M)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>X
+R1-S</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>X
+R6-N</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="n"/>
+      <c r="I5" s="24" t="n"/>
+      <c r="J5" s="24" t="n"/>
+      <c r="K5" s="24" t="n"/>
+      <c r="L5" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R4-S</t>
+        </is>
+      </c>
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R9-N</t>
+        </is>
+      </c>
+      <c r="O5" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Jeff E (M)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>X
+R1-S</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="24" t="n"/>
+      <c r="G6" s="24" t="n"/>
+      <c r="H6" s="24" t="n"/>
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>X
+R8-N</t>
+        </is>
+      </c>
+      <c r="K6" s="24" t="n"/>
+      <c r="L6" s="24" t="n"/>
+      <c r="M6" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R4-N</t>
+        </is>
+      </c>
+      <c r="N6" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R5-S</t>
+        </is>
+      </c>
+      <c r="O6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Dro (M)</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>X
+R1-N</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="n"/>
+      <c r="H7" s="24" t="n"/>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>X
+R8-S</t>
+        </is>
+      </c>
+      <c r="J7" s="24" t="n"/>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>X
+R3-N</t>
+        </is>
+      </c>
+      <c r="L7" s="24" t="n"/>
+      <c r="M7" s="24" t="n"/>
+      <c r="N7" s="24" t="n"/>
+      <c r="O7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Steve (M)</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>X
+R1-N</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="24" t="n"/>
+      <c r="H8" s="24" t="n"/>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>X
+R3-S</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>X
+R6-S</t>
+        </is>
+      </c>
+      <c r="K8" s="24" t="n"/>
+      <c r="L8" s="24" t="n"/>
+      <c r="M8" s="24" t="n"/>
+      <c r="N8" s="24" t="n"/>
+      <c r="O8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>Mich (M)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>X
+R6-N</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>X
+R2-S</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="n"/>
+      <c r="J9" s="24" t="n"/>
+      <c r="K9" s="24" t="n"/>
+      <c r="L9" s="24" t="n"/>
+      <c r="M9" s="24" t="n"/>
+      <c r="N9" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R7-N</t>
+        </is>
+      </c>
+      <c r="O9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Wilfred (M)</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>X
+R2-S</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="24" t="n"/>
+      <c r="J10" s="24" t="n"/>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>X
+R5-N</t>
+        </is>
+      </c>
+      <c r="L10" s="24" t="n"/>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R9-S</t>
+        </is>
+      </c>
+      <c r="N10" s="24" t="n"/>
+      <c r="O10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>Jeff W (M)</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>X
+R8-S</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>X
+R3-S</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="24" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>X
+R2-N</t>
+        </is>
+      </c>
+      <c r="K11" s="24" t="n"/>
+      <c r="L11" s="24" t="n"/>
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="24" t="n"/>
+      <c r="O11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Yu Fon (M)</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>X
+R8-N</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>X
+R6-S</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="n"/>
+      <c r="H12" s="24" t="n"/>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>X
+R2-N</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="24" t="n"/>
+      <c r="L12" s="24" t="n"/>
+      <c r="M12" s="24" t="n"/>
+      <c r="N12" s="24" t="n"/>
+      <c r="O12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>Johnny (M)</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>X
+R3-N</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="24" t="n"/>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>X
+R5-N</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="n"/>
+      <c r="J13" s="24" t="n"/>
+      <c r="K13" s="22" t="n"/>
+      <c r="L13" s="24" t="n"/>
+      <c r="M13" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R7-S</t>
+        </is>
+      </c>
+      <c r="N13" s="24" t="n"/>
+      <c r="O13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Suzan (F) ©</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R4-S</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="24" t="n"/>
+      <c r="F14" s="24" t="n"/>
+      <c r="G14" s="24" t="n"/>
+      <c r="H14" s="24" t="n"/>
+      <c r="I14" s="24" t="n"/>
+      <c r="J14" s="24" t="n"/>
+      <c r="K14" s="24" t="n"/>
+      <c r="L14" s="22" t="n"/>
+      <c r="M14" s="24" t="n"/>
+      <c r="N14" s="24" t="n"/>
+      <c r="O14" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>Rachel (F)</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R4-N</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="24" t="n"/>
+      <c r="G15" s="24" t="n"/>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R9-S</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="n"/>
+      <c r="J15" s="24" t="n"/>
+      <c r="K15" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R7-S</t>
+        </is>
+      </c>
+      <c r="L15" s="24" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="24" t="n"/>
+      <c r="O15" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Molly (F)</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R9-N</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R5-S</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R7-N</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="n"/>
+      <c r="I16" s="24" t="n"/>
+      <c r="J16" s="24" t="n"/>
+      <c r="K16" s="24" t="n"/>
+      <c r="L16" s="24" t="n"/>
+      <c r="M16" s="24" t="n"/>
+      <c r="N16" s="22" t="n"/>
+      <c r="O16" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total Games</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Men's Dbl</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mixed★</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Games in order (round-court)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="C2" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D2" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="33" t="inlineStr">
+        <is>
+          <t>R1-S w/Jeff E,  R4-S★ w/Suzan,  R6-N w/Mich,  R9-N★ w/Molly</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>Jeff E</t>
+        </is>
+      </c>
+      <c r="C3" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D3" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="33" t="inlineStr">
+        <is>
+          <t>R1-S w/Pierre,  R4-N★ w/Rachel,  R5-S★ w/Molly,  R8-N w/Yu Fon</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>Dro</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="33" t="inlineStr">
+        <is>
+          <t>R1-N w/Steve,  R3-N w/Johnny,  R8-S w/Jeff W</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="33" t="inlineStr">
+        <is>
+          <t>R1-N w/Dro,  R3-S w/Jeff W,  R6-S w/Yu Fon</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Mich</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="33" t="inlineStr">
+        <is>
+          <t>R2-S w/Wilfred,  R6-N w/Pierre,  R7-N★ w/Molly</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Wilfred</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="33" t="inlineStr">
+        <is>
+          <t>R2-S w/Mich,  R5-N w/Johnny,  R9-S★ w/Rachel</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>Jeff W</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="33" t="inlineStr">
+        <is>
+          <t>R2-N w/Yu Fon,  R3-S w/Steve,  R8-S w/Dro</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Yu Fon</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="33" t="inlineStr">
+        <is>
+          <t>R2-N w/Jeff W,  R6-S w/Steve,  R8-N w/Jeff E</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Johnny</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="33" t="inlineStr">
+        <is>
+          <t>R3-N w/Dro,  R5-N w/Wilfred,  R7-S★ w/Rachel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Suzan</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>Captain</t>
+        </is>
+      </c>
+      <c r="E11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="37" t="inlineStr">
+        <is>
+          <t>R4-S★ w/Pierre</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="37" t="inlineStr">
+        <is>
+          <t>R4-N★ w/Jeff E,  R7-S★ w/Johnny,  R9-S★ w/Wilfred</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>Molly</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="37" t="inlineStr">
+        <is>
+          <t>R5-S★ w/Jeff E,  R7-N★ w/Mich,  R9-N★ w/Pierre</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Blue Crew (JPL Team) — Pairings Matrix   (X = Men's Doubles  |  M★ = Mixed Doubles  |  C★ = Captain's game)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Captain: Cora (1 game w/ Jay)  ·  Couples: Trevor↔Alexis, Marv↔Carmela, Pierre↔Ivy  ·  No back-to-back games</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>Cora
+(C★)</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>Alexis
+(F)</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>Carmela
+(F)</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>Ivy
+(F)</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>Jay
+(M)</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Marv
+(M)</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>Arman
+(M)</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>Jon
+(M)</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>Trevor
+(M)</t>
+        </is>
+      </c>
+      <c r="L4" s="18" t="inlineStr">
+        <is>
+          <t>Richard
+(M)</t>
+        </is>
+      </c>
+      <c r="M4" s="18" t="inlineStr">
+        <is>
+          <t>Rhon
+(M)</t>
+        </is>
+      </c>
+      <c r="N4" s="18" t="inlineStr">
+        <is>
+          <t>Joe
+(M)</t>
+        </is>
+      </c>
+      <c r="O4" s="18" t="inlineStr">
+        <is>
+          <t>Pierre
+(M)</t>
+        </is>
+      </c>
+      <c r="P4" s="13" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="Q4" s="13" t="inlineStr">
+        <is>
+          <t>Mix★</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>Cora (C★) Captain</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="41" t="inlineStr">
+        <is>
+          <t>C★
+R7-S</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="n"/>
+      <c r="I5" s="24" t="n"/>
+      <c r="J5" s="24" t="n"/>
+      <c r="K5" s="24" t="n"/>
+      <c r="L5" s="24" t="n"/>
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="24" t="n"/>
+      <c r="O5" s="24" t="n"/>
+      <c r="P5" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Alexis (F)</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="24" t="n"/>
+      <c r="G6" s="24" t="n"/>
+      <c r="H6" s="24" t="n"/>
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="24" t="n"/>
+      <c r="K6" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R5-S,R9-S</t>
+        </is>
+      </c>
+      <c r="L6" s="24" t="n"/>
+      <c r="M6" s="24" t="n"/>
+      <c r="N6" s="24" t="n"/>
+      <c r="O6" s="24" t="n"/>
+      <c r="P6" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Carmela (F)</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="24" t="n"/>
+      <c r="G7" s="24" t="n"/>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R4-N,R9-N</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="n"/>
+      <c r="J7" s="24" t="n"/>
+      <c r="K7" s="24" t="n"/>
+      <c r="L7" s="24" t="n"/>
+      <c r="M7" s="24" t="n"/>
+      <c r="N7" s="24" t="n"/>
+      <c r="O7" s="24" t="n"/>
+      <c r="P7" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Ivy (F)</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="24" t="n"/>
+      <c r="H8" s="24" t="n"/>
+      <c r="I8" s="24" t="n"/>
+      <c r="J8" s="24" t="n"/>
+      <c r="K8" s="24" t="n"/>
+      <c r="L8" s="24" t="n"/>
+      <c r="M8" s="24" t="n"/>
+      <c r="N8" s="24" t="n"/>
+      <c r="O8" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R4-S,R7-N</t>
+        </is>
+      </c>
+      <c r="P8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>Jay (M)</t>
+        </is>
+      </c>
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>C★
+R7-S</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="24" t="n"/>
+      <c r="I9" s="24" t="n"/>
+      <c r="J9" s="24" t="n"/>
+      <c r="K9" s="24" t="n"/>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t>X
+R3-N</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>X
+R5-N</t>
+        </is>
+      </c>
+      <c r="N9" s="24" t="n"/>
+      <c r="O9" s="24" t="n"/>
+      <c r="P9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Marv (M)</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R4-N,R9-N</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="24" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="24" t="n"/>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>X
+R2-N</t>
+        </is>
+      </c>
+      <c r="K10" s="24" t="n"/>
+      <c r="L10" s="24" t="n"/>
+      <c r="M10" s="24" t="n"/>
+      <c r="N10" s="24" t="n"/>
+      <c r="O10" s="24" t="n"/>
+      <c r="P10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>Arman (M)</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="24" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="24" t="n"/>
+      <c r="K11" s="24" t="n"/>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t>X
+R6-S</t>
+        </is>
+      </c>
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="23" t="inlineStr">
+        <is>
+          <t>X
+R8-S</t>
+        </is>
+      </c>
+      <c r="O11" s="23" t="inlineStr">
+        <is>
+          <t>X
+R2-S</t>
+        </is>
+      </c>
+      <c r="P11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Jon (M)</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="24" t="n"/>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>X
+R2-N</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="24" t="n"/>
+      <c r="L12" s="24" t="n"/>
+      <c r="M12" s="23" t="inlineStr">
+        <is>
+          <t>X
+R8-N</t>
+        </is>
+      </c>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t>X
+R6-N</t>
+        </is>
+      </c>
+      <c r="O12" s="24" t="n"/>
+      <c r="P12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>Trevor (M)</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R5-S,R9-S</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="24" t="n"/>
+      <c r="H13" s="24" t="n"/>
+      <c r="I13" s="24" t="n"/>
+      <c r="J13" s="24" t="n"/>
+      <c r="K13" s="22" t="n"/>
+      <c r="L13" s="24" t="n"/>
+      <c r="M13" s="23" t="inlineStr">
+        <is>
+          <t>X
+R1-S</t>
+        </is>
+      </c>
+      <c r="N13" s="24" t="n"/>
+      <c r="O13" s="24" t="n"/>
+      <c r="P13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Richard (M)</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="24" t="n"/>
+      <c r="F14" s="24" t="n"/>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>X
+R3-N</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="n"/>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>X
+R6-S</t>
+        </is>
+      </c>
+      <c r="J14" s="24" t="n"/>
+      <c r="K14" s="24" t="n"/>
+      <c r="L14" s="22" t="n"/>
+      <c r="M14" s="24" t="n"/>
+      <c r="N14" s="23" t="inlineStr">
+        <is>
+          <t>X
+R1-N</t>
+        </is>
+      </c>
+      <c r="O14" s="24" t="n"/>
+      <c r="P14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Rhon (M)</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="24" t="n"/>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>X
+R5-N</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="n"/>
+      <c r="I15" s="24" t="n"/>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>X
+R8-N</t>
+        </is>
+      </c>
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>X
+R1-S</t>
+        </is>
+      </c>
+      <c r="L15" s="24" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="23" t="inlineStr">
+        <is>
+          <t>X
+R3-S</t>
+        </is>
+      </c>
+      <c r="O15" s="24" t="n"/>
+      <c r="P15" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Joe (M)</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="24" t="n"/>
+      <c r="H16" s="24" t="n"/>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>X
+R8-S</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>X
+R6-N</t>
+        </is>
+      </c>
+      <c r="K16" s="24" t="n"/>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t>X
+R1-N</t>
+        </is>
+      </c>
+      <c r="M16" s="23" t="inlineStr">
+        <is>
+          <t>X
+R3-S</t>
+        </is>
+      </c>
+      <c r="N16" s="22" t="n"/>
+      <c r="O16" s="24" t="n"/>
+      <c r="P16" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q16" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>Pierre (M)</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>M★
+R4-S,R7-N</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="n"/>
+      <c r="H17" s="24" t="n"/>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>X
+R2-S</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="n"/>
+      <c r="K17" s="24" t="n"/>
+      <c r="L17" s="24" t="n"/>
+      <c r="M17" s="24" t="n"/>
+      <c r="N17" s="24" t="n"/>
+      <c r="O17" s="22" t="n"/>
+      <c r="P17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total Games</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Men's Dbl</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mixed★</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Games in order (round-court)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="45" t="inlineStr">
+        <is>
+          <t>Cora</t>
+        </is>
+      </c>
+      <c r="C2" s="44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D2" s="44" t="inlineStr">
+        <is>
+          <t>Captain</t>
+        </is>
+      </c>
+      <c r="E2" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="47" t="inlineStr">
+        <is>
+          <t>R7-S★ w/Jay</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>Alexis</t>
+        </is>
+      </c>
+      <c r="C3" s="34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D3" s="34" t="inlineStr">
+        <is>
+          <t>Couple</t>
+        </is>
+      </c>
+      <c r="E3" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="37" t="inlineStr">
+        <is>
+          <t>R5-S★ w/Trevor,  R9-S★ w/Trevor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>Carmela</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D4" s="34" t="inlineStr">
+        <is>
+          <t>Couple</t>
+        </is>
+      </c>
+      <c r="E4" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="37" t="inlineStr">
+        <is>
+          <t>R4-N★ w/Marv,  R9-N★ w/Marv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Ivy</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="inlineStr">
+        <is>
+          <t>Couple</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="37" t="inlineStr">
+        <is>
+          <t>R4-S★ w/Pierre,  R7-N★ w/Pierre</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="33" t="inlineStr">
+        <is>
+          <t>R3-N w/Richard,  R5-N w/Rhon,  R7-S★ w/Cora</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Marv</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>Couple</t>
+        </is>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="33" t="inlineStr">
+        <is>
+          <t>R2-N w/Jon,  R4-N★ w/Carmela,  R9-N★ w/Carmela</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>Arman</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="33" t="inlineStr">
+        <is>
+          <t>R2-S w/Pierre,  R6-S w/Richard,  R8-S w/Joe</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Jon</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="33" t="inlineStr">
+        <is>
+          <t>R2-N w/Marv,  R6-N w/Joe,  R8-N w/Rhon</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>Couple</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="33" t="inlineStr">
+        <is>
+          <t>R1-S w/Rhon,  R5-S★ w/Alexis,  R9-S★ w/Alexis</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="33" t="inlineStr">
+        <is>
+          <t>R1-N w/Joe,  R3-N w/Jay,  R6-S w/Arman</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="49" t="inlineStr">
+        <is>
+          <t>Rhon</t>
+        </is>
+      </c>
+      <c r="C12" s="48" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D12" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="51" t="inlineStr">
+        <is>
+          <t>R1-S w/Trevor,  R3-S w/Joe,  R5-N w/Jay,  R8-N w/Jon</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>Joe</t>
+        </is>
+      </c>
+      <c r="C13" s="48" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D13" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="51" t="inlineStr">
+        <is>
+          <t>R1-N w/Richard,  R3-S w/Rhon,  R6-N w/Jon,  R8-S w/Arman</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="30" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>Couple</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="33" t="inlineStr">
+        <is>
+          <t>R2-S w/Arman,  R4-S★ w/Ivy,  R7-N★ w/Ivy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/backend/ATH_Open_Sheets_Template.xlsx
+++ b/backend/ATH_Open_Sheets_Template.xlsx
@@ -1605,7 +1605,11 @@
           <t>Pierre</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
           <t>B</t>
@@ -3069,7 +3073,7 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Pierre Y</t>
         </is>
       </c>
       <c r="I6" s="14" t="n"/>
@@ -3228,7 +3232,7 @@
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Pierre Y</t>
         </is>
       </c>
       <c r="H10" s="15" t="inlineStr">
@@ -3519,7 +3523,7 @@
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Pierre Y</t>
         </is>
       </c>
       <c r="H17" s="15" t="inlineStr">
@@ -4972,7 +4976,7 @@
       </c>
       <c r="O4" s="18" t="inlineStr">
         <is>
-          <t>Pierre
+          <t>Pierre Y
 (M)</t>
         </is>
       </c>
@@ -5491,7 +5495,7 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>Pierre (M)</t>
+          <t>Pierre Y (M)</t>
         </is>
       </c>
       <c r="C17" s="24" t="n"/>
@@ -5726,7 +5730,7 @@
       </c>
       <c r="H5" s="37" t="inlineStr">
         <is>
-          <t>R4-S★ w/Pierre,  R7-N★ w/Pierre</t>
+          <t>R4-S★ w/Pierre Y,  R7-N★ w/Pierre Y</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5832,7 @@
       </c>
       <c r="H8" s="33" t="inlineStr">
         <is>
-          <t>R2-S w/Pierre,  R6-S w/Richard,  R8-S w/Joe</t>
+          <t>R2-S w/Pierre Y,  R6-S w/Richard,  R8-S w/Joe</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6012,7 @@
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Pierre Y</t>
         </is>
       </c>
       <c r="C14" s="30" t="inlineStr">
